--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5555" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5555" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedEncounter</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedEncounter</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:21:37+00:00</t>
+    <t>2025-03-11T16:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ELGA</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ELGA (https://www.elga.gv.at/)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -458,17 +458,14 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Encounter.extension:unfalldatum</t>
-  </si>
-  <si>
-    <t>unfalldatum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-unfalldatum}
+    <t>Encounter.extension:Unfalldatum</t>
+  </si>
+  <si>
+    <t>Unfalldatum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-unfalldatum}
 </t>
-  </si>
-  <si>
-    <t>Unfalldatum</t>
   </si>
   <si>
     <t>MOPED Extension für das Ereignis-/Unfalldatum.</t>
@@ -1110,7 +1107,7 @@
     <t>Behandlungsart</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-behandlungsart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/Behandlungsart</t>
   </si>
   <si>
     <t>Encounter.class:Behandlungsart.id</t>
@@ -1149,7 +1146,7 @@
     <t>Encounter.class.coding.system</t>
   </si>
   <si>
-    <t>http://tbd.at/MOPED-encounter-behandlungsart</t>
+    <t>https://elga.moped.at/CodeSystem/BehandlungsartCS</t>
   </si>
   <si>
     <t>Encounter.class:Behandlungsart.coding.version</t>
@@ -1188,7 +1185,7 @@
     <t>Aufnahmeart2</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-aufnahmeart2-valueset</t>
+    <t>https://elga.moped.at/ValueSet/Aufnahmeart2</t>
   </si>
   <si>
     <t>Encounter.class:Aufnahmeart2.id</t>
@@ -1209,7 +1206,7 @@
     <t>Encounter.class:Aufnahmeart2.coding.system</t>
   </si>
   <si>
-    <t>http://tbd.at/moped-ext-aufnahmeart2</t>
+    <t>https://elga.moped.at/CodeSystem/Aufnahmeart2CS</t>
   </si>
   <si>
     <t>Encounter.class:Aufnahmeart2.coding.version</t>
@@ -1261,6 +1258,14 @@
   </si>
   <si>
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://elga.moped.at/CodeSystem/MopedEncounterTypesCS"/&gt;
+    &lt;code value="ENC"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>A specific code indicating type of service provided</t>
@@ -1433,10 +1438,6 @@
   </si>
   <si>
     <t>Encounter.serviceProvider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedOrganizationAbteilung)
-</t>
   </si>
   <si>
     <t>The organization (facility) responsible for this encounter</t>
@@ -1872,7 +1873,7 @@
     <t>Encounter.reason:Ursache.value</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-ursache-valueset</t>
+    <t>https://elga.moped.at/ValueSet/UrsacheValueSet</t>
   </si>
   <si>
     <t>Encounter.diagnosis</t>
@@ -1934,10 +1935,10 @@
     <t>Role that this diagnosis has within the encounter (e.g. admission, billing, discharge …).</t>
   </si>
   <si>
-    <t>Code für den Typ der LKF Diagnose, der angibt ob es sich um eine Haupt- oder Nebendiagnose handelt</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/CodeSystem-lkf-diagnose-typ.html</t>
+    <t>The type of diagnosis this condition represents.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diagnosis-use</t>
   </si>
   <si>
     <t>DG1-6 (Diagnosis Type)</t>
@@ -1946,7 +1947,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedAccount)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedAccount)
 </t>
   </si>
   <si>
@@ -2069,7 +2070,7 @@
     <t>aufnahmeart</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-aufnahmeart}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-aufnahmeart}
 </t>
   </si>
   <si>
@@ -2085,7 +2086,7 @@
     <t>transportart</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-transportart}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-transportart}
 </t>
   </si>
   <si>
@@ -2185,7 +2186,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-entlassungsart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/Entlassungsart</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -2615,8 +2616,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.57421875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="74.65625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.25390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3691,10 +3692,10 @@
         <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3774,14 +3775,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3803,16 +3804,16 @@
         <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3861,7 +3862,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3890,10 +3891,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3916,13 +3917,13 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3961,7 +3962,7 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
@@ -3971,7 +3972,7 @@
         <v>139</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3986,27 +3987,27 @@
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -4028,13 +4029,13 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -4085,7 +4086,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -4100,24 +4101,24 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>162</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4143,10 +4144,10 @@
         <v>90</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4197,7 +4198,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -4206,19 +4207,19 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
@@ -4226,14 +4227,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4255,13 +4256,13 @@
         <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N15" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4302,7 +4303,7 @@
         <v>138</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>20</v>
@@ -4311,7 +4312,7 @@
         <v>139</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4332,7 +4333,7 @@
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -4340,10 +4341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4369,16 +4370,16 @@
         <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -4406,28 +4407,28 @@
         <v>112</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4448,7 +4449,7 @@
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>133</v>
@@ -4456,10 +4457,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4482,19 +4483,19 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -4523,25 +4524,25 @@
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4562,18 +4563,18 @@
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4599,10 +4600,10 @@
         <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4653,7 +4654,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4662,19 +4663,19 @@
         <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
@@ -4682,14 +4683,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4711,13 +4712,13 @@
         <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N19" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4758,7 +4759,7 @@
         <v>138</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>20</v>
@@ -4767,7 +4768,7 @@
         <v>139</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4788,7 +4789,7 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>20</v>
@@ -4796,10 +4797,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4822,19 +4823,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4883,7 +4884,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4904,18 +4905,18 @@
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4941,10 +4942,10 @@
         <v>90</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4995,7 +4996,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -5004,19 +5005,19 @@
         <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
@@ -5024,14 +5025,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5053,13 +5054,13 @@
         <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M22" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N22" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5100,7 +5101,7 @@
         <v>138</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
@@ -5109,7 +5110,7 @@
         <v>139</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5130,7 +5131,7 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -5138,10 +5139,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5167,16 +5168,16 @@
         <v>102</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -5225,7 +5226,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5246,18 +5247,18 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5280,16 +5281,16 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5339,7 +5340,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5360,18 +5361,18 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5397,63 +5398,63 @@
         <v>108</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5462,7 +5463,7 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>100</v>
@@ -5474,18 +5475,18 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5508,17 +5509,17 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5567,7 +5568,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5576,7 +5577,7 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>100</v>
@@ -5588,18 +5589,18 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5622,19 +5623,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5683,7 +5684,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5704,18 +5705,18 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5738,19 +5739,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5799,7 +5800,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5820,18 +5821,18 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5857,16 +5858,16 @@
         <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5879,43 +5880,43 @@
         <v>20</v>
       </c>
       <c r="T29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5936,18 +5937,18 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5970,16 +5971,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5993,43 +5994,43 @@
         <v>20</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -6038,7 +6039,7 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
@@ -6050,18 +6051,18 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6084,13 +6085,13 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6141,7 +6142,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6162,18 +6163,18 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6196,16 +6197,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6255,7 +6256,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6276,21 +6277,21 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>20</v>
@@ -6312,13 +6313,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6369,7 +6370,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6384,24 +6385,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>162</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6427,10 +6428,10 @@
         <v>90</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6481,7 +6482,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6490,19 +6491,19 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -6510,14 +6511,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6539,13 +6540,13 @@
         <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N35" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6586,7 +6587,7 @@
         <v>138</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>20</v>
@@ -6595,7 +6596,7 @@
         <v>139</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6616,7 +6617,7 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -6624,10 +6625,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6653,16 +6654,16 @@
         <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6690,28 +6691,28 @@
         <v>112</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z36" t="s" s="2">
+      <c r="AA36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6732,7 +6733,7 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>133</v>
@@ -6740,10 +6741,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6766,19 +6767,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6807,25 +6808,25 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6846,18 +6847,18 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6883,10 +6884,10 @@
         <v>90</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6937,7 +6938,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6946,19 +6947,19 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6966,14 +6967,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6995,13 +6996,13 @@
         <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N39" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7042,7 +7043,7 @@
         <v>138</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>20</v>
@@ -7051,7 +7052,7 @@
         <v>139</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7072,7 +7073,7 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -7080,10 +7081,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7106,19 +7107,19 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7167,7 +7168,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7188,18 +7189,18 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7225,10 +7226,10 @@
         <v>90</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7279,7 +7280,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7288,19 +7289,19 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -7308,14 +7309,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7337,13 +7338,13 @@
         <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N42" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7384,7 +7385,7 @@
         <v>138</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>20</v>
@@ -7393,7 +7394,7 @@
         <v>139</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7414,7 +7415,7 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -7422,10 +7423,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7451,16 +7452,16 @@
         <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7509,7 +7510,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7530,18 +7531,18 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7564,16 +7565,16 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7623,7 +7624,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7644,18 +7645,18 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7681,21 +7682,21 @@
         <v>108</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>20</v>
@@ -7737,7 +7738,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7746,7 +7747,7 @@
         <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>100</v>
@@ -7758,18 +7759,18 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7792,17 +7793,17 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7851,7 +7852,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7860,7 +7861,7 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
@@ -7872,18 +7873,18 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7906,19 +7907,19 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7967,7 +7968,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7988,18 +7989,18 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8022,19 +8023,19 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -8083,7 +8084,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8104,18 +8105,18 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8141,16 +8142,16 @@
         <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -8163,43 +8164,43 @@
         <v>20</v>
       </c>
       <c r="T49" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8220,18 +8221,18 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8254,16 +8255,16 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8277,43 +8278,43 @@
         <v>20</v>
       </c>
       <c r="T50" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8322,7 +8323,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -8334,18 +8335,18 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8368,13 +8369,13 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8425,7 +8426,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8446,18 +8447,18 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8480,16 +8481,16 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8539,7 +8540,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8560,18 +8561,18 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8597,13 +8598,13 @@
         <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8632,11 +8633,11 @@
         <v>112</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8653,7 +8654,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>88</v>
@@ -8668,24 +8669,24 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>341</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8708,13 +8709,13 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8741,19 +8742,19 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="Y54" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="Y54" t="s" s="2">
+      <c r="Z54" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Z54" t="s" s="2">
+      <c r="AA54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB54" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
@@ -8763,7 +8764,7 @@
         <v>139</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8781,24 +8782,24 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>20</v>
@@ -8820,13 +8821,13 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8857,7 +8858,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8875,7 +8876,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8893,21 +8894,21 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8933,10 +8934,10 @@
         <v>90</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8987,7 +8988,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8996,19 +8997,19 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>20</v>
@@ -9016,14 +9017,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9045,13 +9046,13 @@
         <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N57" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9092,7 +9093,7 @@
         <v>138</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>20</v>
@@ -9101,7 +9102,7 @@
         <v>139</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9122,7 +9123,7 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>20</v>
@@ -9130,10 +9131,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9156,19 +9157,19 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9217,7 +9218,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9238,18 +9239,18 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9275,10 +9276,10 @@
         <v>90</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9329,7 +9330,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9338,19 +9339,19 @@
         <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>20</v>
@@ -9358,14 +9359,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9387,13 +9388,13 @@
         <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9434,7 +9435,7 @@
         <v>138</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>20</v>
@@ -9443,7 +9444,7 @@
         <v>139</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9464,7 +9465,7 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>20</v>
@@ -9472,10 +9473,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9501,16 +9502,16 @@
         <v>102</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9520,7 +9521,7 @@
         <v>20</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>20</v>
@@ -9559,7 +9560,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9580,18 +9581,18 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9614,16 +9615,16 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9673,7 +9674,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9694,18 +9695,18 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9731,14 +9732,14 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9787,7 +9788,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9796,7 +9797,7 @@
         <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>100</v>
@@ -9808,18 +9809,18 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9842,17 +9843,17 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9901,7 +9902,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9910,7 +9911,7 @@
         <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>100</v>
@@ -9922,18 +9923,18 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9956,19 +9957,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -10017,7 +10018,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10038,18 +10039,18 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10072,19 +10073,19 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10133,7 +10134,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10154,21 +10155,21 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="C67" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>20</v>
@@ -10190,13 +10191,13 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10227,7 +10228,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -10245,7 +10246,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10263,21 +10264,21 @@
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10303,10 +10304,10 @@
         <v>90</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10357,7 +10358,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10366,19 +10367,19 @@
         <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
@@ -10386,14 +10387,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10415,13 +10416,13 @@
         <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N69" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10462,7 +10463,7 @@
         <v>138</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>20</v>
@@ -10471,7 +10472,7 @@
         <v>139</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10492,7 +10493,7 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
@@ -10500,10 +10501,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10526,19 +10527,19 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10587,7 +10588,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10608,18 +10609,18 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10645,10 +10646,10 @@
         <v>90</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10699,7 +10700,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10708,19 +10709,19 @@
         <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>20</v>
@@ -10728,14 +10729,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10757,13 +10758,13 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N72" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10804,7 +10805,7 @@
         <v>138</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>20</v>
@@ -10813,7 +10814,7 @@
         <v>139</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10834,7 +10835,7 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>20</v>
@@ -10842,10 +10843,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10871,16 +10872,16 @@
         <v>102</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10890,7 +10891,7 @@
         <v>20</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>20</v>
@@ -10929,7 +10930,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10950,18 +10951,18 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10984,16 +10985,16 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11043,7 +11044,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11064,18 +11065,18 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11101,14 +11102,14 @@
         <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11157,7 +11158,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11166,7 +11167,7 @@
         <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>100</v>
@@ -11178,18 +11179,18 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11212,17 +11213,17 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11271,7 +11272,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11280,7 +11281,7 @@
         <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>100</v>
@@ -11292,18 +11293,18 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11326,19 +11327,19 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11387,7 +11388,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11408,18 +11409,18 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11442,19 +11443,19 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -11503,7 +11504,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11524,18 +11525,18 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11558,13 +11559,13 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11591,14 +11592,14 @@
         <v>20</v>
       </c>
       <c r="X79" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z79" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="Y79" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="AA79" t="s" s="2">
         <v>20</v>
       </c>
@@ -11615,7 +11616,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11633,21 +11634,21 @@
         <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AN79" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>400</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11670,16 +11671,16 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11690,7 +11691,7 @@
         <v>20</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>20</v>
+        <v>404</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>20</v>
@@ -11705,7 +11706,7 @@
         <v>20</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y80" t="s" s="2">
         <v>405</v>
@@ -11729,7 +11730,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11817,7 +11818,7 @@
         <v>20</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y81" t="s" s="2">
         <v>415</v>
@@ -11862,7 +11863,7 @@
         <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>417</v>
@@ -12010,7 +12011,7 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>429</v>
@@ -12045,7 +12046,7 @@
         <v>20</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y83" t="s" s="2">
         <v>432</v>
@@ -12202,7 +12203,7 @@
         <v>438</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>439</v>
@@ -12426,7 +12427,7 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>20</v>
@@ -12574,13 +12575,13 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12646,24 +12647,24 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AL88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AN88" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>464</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12686,16 +12687,16 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12745,7 +12746,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12757,27 +12758,27 @@
         <v>20</v>
       </c>
       <c r="AJ89" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AK89" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AK89" t="s" s="2">
+      <c r="AL89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AL89" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM89" t="s" s="2">
+      <c r="AN89" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>473</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12800,13 +12801,13 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12857,7 +12858,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12866,19 +12867,19 @@
         <v>88</v>
       </c>
       <c r="AI90" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>20</v>
@@ -12886,14 +12887,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12915,13 +12916,13 @@
         <v>135</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N91" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12971,7 +12972,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12992,7 +12993,7 @@
         <v>20</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>20</v>
@@ -13000,14 +13001,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13029,16 +13030,16 @@
         <v>135</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="N92" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O92" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13087,7 +13088,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13116,10 +13117,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13142,16 +13143,16 @@
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13177,14 +13178,14 @@
         <v>20</v>
       </c>
       <c r="X93" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="Y93" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>486</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>20</v>
       </c>
@@ -13201,7 +13202,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13210,30 +13211,30 @@
         <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AL93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>490</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13256,13 +13257,13 @@
         <v>20</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13313,7 +13314,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13334,18 +13335,18 @@
         <v>20</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>495</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13368,16 +13369,16 @@
         <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13427,7 +13428,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13436,30 +13437,30 @@
         <v>88</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>503</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13482,13 +13483,13 @@
         <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13539,7 +13540,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13560,18 +13561,18 @@
         <v>20</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>509</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13594,16 +13595,16 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13653,7 +13654,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13682,10 +13683,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13708,16 +13709,16 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13767,7 +13768,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13782,24 +13783,24 @@
         <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AL98" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AL98" t="s" s="2">
+      <c r="AM98" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AM98" t="s" s="2">
+      <c r="AN98" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>522</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13822,13 +13823,13 @@
         <v>20</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13879,7 +13880,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13903,15 +13904,15 @@
         <v>20</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13934,13 +13935,13 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13991,7 +13992,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14015,15 +14016,15 @@
         <v>20</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14046,16 +14047,16 @@
         <v>20</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14105,7 +14106,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14120,24 +14121,24 @@
         <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM101" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>538</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14160,16 +14161,16 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14207,7 +14208,7 @@
         <v>20</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
@@ -14217,7 +14218,7 @@
         <v>139</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14246,10 +14247,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14272,13 +14273,13 @@
         <v>20</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14329,7 +14330,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14338,19 +14339,19 @@
         <v>88</v>
       </c>
       <c r="AI103" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>20</v>
@@ -14358,14 +14359,14 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14387,13 +14388,13 @@
         <v>135</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N104" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14443,7 +14444,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14464,7 +14465,7 @@
         <v>20</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>20</v>
@@ -14472,14 +14473,14 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14501,16 +14502,16 @@
         <v>135</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M105" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="N105" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O105" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>20</v>
@@ -14559,7 +14560,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14588,10 +14589,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14614,13 +14615,13 @@
         <v>89</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14647,11 +14648,11 @@
         <v>20</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>20</v>
@@ -14669,7 +14670,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14698,14 +14699,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -14724,13 +14725,13 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14757,14 +14758,14 @@
         <v>20</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>557</v>
-      </c>
       <c r="AA107" t="s" s="2">
         <v>20</v>
       </c>
@@ -14781,7 +14782,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14796,27 +14797,27 @@
         <v>100</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AL107" t="s" s="2">
+      <c r="AM107" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="AM107" t="s" s="2">
+      <c r="AN107" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>561</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>20</v>
@@ -14838,16 +14839,16 @@
         <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M108" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14897,7 +14898,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14926,10 +14927,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14952,13 +14953,13 @@
         <v>20</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15009,7 +15010,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15018,19 +15019,19 @@
         <v>88</v>
       </c>
       <c r="AI109" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>20</v>
@@ -15038,14 +15039,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15067,13 +15068,13 @@
         <v>135</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M110" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N110" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15123,7 +15124,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15144,7 +15145,7 @@
         <v>20</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>20</v>
@@ -15152,14 +15153,14 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15181,16 +15182,16 @@
         <v>135</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M111" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="N111" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O111" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -15239,7 +15240,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15268,10 +15269,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15294,13 +15295,13 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15331,7 +15332,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>20</v>
@@ -15349,7 +15350,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15378,10 +15379,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15407,10 +15408,10 @@
         <v>90</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15461,7 +15462,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15470,19 +15471,19 @@
         <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM113" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>20</v>
@@ -15490,14 +15491,14 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15519,13 +15520,13 @@
         <v>135</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M114" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N114" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15566,7 +15567,7 @@
         <v>138</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>20</v>
@@ -15575,7 +15576,7 @@
         <v>139</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15596,7 +15597,7 @@
         <v>20</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>20</v>
@@ -15604,10 +15605,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15630,19 +15631,19 @@
         <v>89</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>20</v>
@@ -15691,7 +15692,7 @@
         <v>20</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15712,18 +15713,18 @@
         <v>20</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15749,10 +15750,10 @@
         <v>90</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15803,7 +15804,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15812,19 +15813,19 @@
         <v>88</v>
       </c>
       <c r="AI116" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM116" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>20</v>
@@ -15832,14 +15833,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15861,13 +15862,13 @@
         <v>135</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M117" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N117" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15908,7 +15909,7 @@
         <v>138</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>20</v>
@@ -15917,7 +15918,7 @@
         <v>139</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15938,7 +15939,7 @@
         <v>20</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>20</v>
@@ -15946,10 +15947,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B118" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15975,16 +15976,16 @@
         <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>20</v>
@@ -16033,7 +16034,7 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16054,18 +16055,18 @@
         <v>20</v>
       </c>
       <c r="AM118" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN118" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B119" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16088,16 +16089,16 @@
         <v>89</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16147,7 +16148,7 @@
         <v>20</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16168,18 +16169,18 @@
         <v>20</v>
       </c>
       <c r="AM119" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN119" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B120" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16205,21 +16206,21 @@
         <v>108</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>20</v>
@@ -16261,7 +16262,7 @@
         <v>20</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16270,7 +16271,7 @@
         <v>88</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>100</v>
@@ -16282,18 +16283,18 @@
         <v>20</v>
       </c>
       <c r="AM120" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AN120" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B121" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16316,17 +16317,17 @@
         <v>89</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>20</v>
@@ -16375,7 +16376,7 @@
         <v>20</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16384,7 +16385,7 @@
         <v>88</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>100</v>
@@ -16396,18 +16397,18 @@
         <v>20</v>
       </c>
       <c r="AM121" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B122" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16430,19 +16431,19 @@
         <v>89</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>20</v>
@@ -16491,7 +16492,7 @@
         <v>20</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16512,18 +16513,18 @@
         <v>20</v>
       </c>
       <c r="AM122" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16546,19 +16547,19 @@
         <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>20</v>
@@ -16607,7 +16608,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16628,22 +16629,22 @@
         <v>20</v>
       </c>
       <c r="AM123" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -16662,13 +16663,13 @@
         <v>89</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16699,7 +16700,7 @@
       </c>
       <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>20</v>
@@ -16717,7 +16718,7 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16732,24 +16733,24 @@
         <v>100</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL124" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AL124" t="s" s="2">
+      <c r="AM124" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="AM124" t="s" s="2">
+      <c r="AN124" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>561</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16772,16 +16773,16 @@
         <v>89</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16831,7 +16832,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16852,7 +16853,7 @@
         <v>20</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>20</v>
@@ -16860,10 +16861,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16886,13 +16887,13 @@
         <v>20</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16943,7 +16944,7 @@
         <v>20</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16952,19 +16953,19 @@
         <v>88</v>
       </c>
       <c r="AI126" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM126" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>20</v>
@@ -16972,14 +16973,14 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -17001,13 +17002,13 @@
         <v>135</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M127" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N127" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17057,7 +17058,7 @@
         <v>20</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17078,7 +17079,7 @@
         <v>20</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>20</v>
@@ -17086,14 +17087,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17115,16 +17116,16 @@
         <v>135</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M128" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="N128" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O128" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>20</v>
@@ -17173,7 +17174,7 @@
         <v>20</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17202,14 +17203,14 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -17228,13 +17229,13 @@
         <v>89</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17261,11 +17262,11 @@
         <v>20</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>20</v>
@@ -17283,7 +17284,7 @@
         <v>20</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17298,24 +17299,24 @@
         <v>100</v>
       </c>
       <c r="AK129" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL129" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AL129" t="s" s="2">
-        <v>559</v>
-      </c>
       <c r="AM129" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AN129" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>609</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17338,13 +17339,13 @@
         <v>20</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17371,14 +17372,14 @@
         <v>20</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>112</v>
+        <v>344</v>
       </c>
       <c r="Y130" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="Z130" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="Z130" t="s" s="2">
-        <v>614</v>
-      </c>
       <c r="AA130" t="s" s="2">
         <v>20</v>
       </c>
@@ -17395,7 +17396,7 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17416,18 +17417,18 @@
         <v>20</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17438,7 +17439,7 @@
         <v>78</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>20</v>
@@ -17450,16 +17451,16 @@
         <v>20</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L131" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="M131" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -17509,7 +17510,7 @@
         <v>20</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17530,7 +17531,7 @@
         <v>20</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>20</v>
@@ -17538,10 +17539,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17564,19 +17565,19 @@
         <v>20</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="N132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>20</v>
@@ -17601,14 +17602,14 @@
         <v>20</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y132" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="Z132" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="Z132" t="s" s="2">
-        <v>628</v>
-      </c>
       <c r="AA132" t="s" s="2">
         <v>20</v>
       </c>
@@ -17625,7 +17626,7 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17646,18 +17647,18 @@
         <v>20</v>
       </c>
       <c r="AM132" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>630</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17680,13 +17681,13 @@
         <v>20</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17713,14 +17714,14 @@
         <v>20</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y133" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="Z133" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="Z133" t="s" s="2">
-        <v>635</v>
-      </c>
       <c r="AA133" t="s" s="2">
         <v>20</v>
       </c>
@@ -17737,7 +17738,7 @@
         <v>20</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17758,18 +17759,18 @@
         <v>20</v>
       </c>
       <c r="AM133" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>637</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17792,16 +17793,16 @@
         <v>20</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17827,14 +17828,14 @@
         <v>20</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="Z134" t="s" s="2">
-        <v>643</v>
-      </c>
       <c r="AA134" t="s" s="2">
         <v>20</v>
       </c>
@@ -17851,7 +17852,7 @@
         <v>20</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17872,18 +17873,18 @@
         <v>20</v>
       </c>
       <c r="AM134" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>645</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17906,16 +17907,16 @@
         <v>20</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17965,7 +17966,7 @@
         <v>20</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17986,7 +17987,7 @@
         <v>20</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>20</v>
@@ -17994,10 +17995,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18020,13 +18021,13 @@
         <v>20</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18077,7 +18078,7 @@
         <v>20</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18086,19 +18087,19 @@
         <v>88</v>
       </c>
       <c r="AI136" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM136" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>20</v>
@@ -18106,10 +18107,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18187,7 +18188,7 @@
         <v>139</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -18216,13 +18217,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C138" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>20</v>
@@ -18244,13 +18245,13 @@
         <v>20</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="L138" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="L138" t="s" s="2">
+      <c r="M138" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -18301,7 +18302,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -18330,13 +18331,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C139" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>20</v>
@@ -18358,13 +18359,13 @@
         <v>20</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18415,7 +18416,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18444,14 +18445,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18473,16 +18474,16 @@
         <v>135</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M140" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="N140" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O140" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>20</v>
@@ -18531,7 +18532,7 @@
         <v>20</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18560,10 +18561,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18586,13 +18587,13 @@
         <v>20</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18643,7 +18644,7 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18664,18 +18665,18 @@
         <v>20</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18698,13 +18699,13 @@
         <v>20</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18755,7 +18756,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18776,7 +18777,7 @@
         <v>20</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>20</v>
@@ -18784,10 +18785,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18810,13 +18811,13 @@
         <v>20</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -18843,14 +18844,14 @@
         <v>20</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="Z143" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="Z143" t="s" s="2">
-        <v>676</v>
-      </c>
       <c r="AA143" t="s" s="2">
         <v>20</v>
       </c>
@@ -18867,7 +18868,7 @@
         <v>20</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -18888,18 +18889,18 @@
         <v>20</v>
       </c>
       <c r="AM143" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AN143" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>678</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18922,13 +18923,13 @@
         <v>20</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -18955,14 +18956,14 @@
         <v>20</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y144" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="Z144" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="Z144" t="s" s="2">
-        <v>683</v>
-      </c>
       <c r="AA144" t="s" s="2">
         <v>20</v>
       </c>
@@ -18979,7 +18980,7 @@
         <v>20</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -19000,18 +19001,18 @@
         <v>20</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19034,13 +19035,13 @@
         <v>20</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19091,7 +19092,7 @@
         <v>20</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19112,18 +19113,18 @@
         <v>20</v>
       </c>
       <c r="AM145" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AN145" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>689</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19146,13 +19147,13 @@
         <v>20</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -19183,7 +19184,7 @@
       </c>
       <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>20</v>
@@ -19201,7 +19202,7 @@
         <v>20</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -19222,18 +19223,18 @@
         <v>20</v>
       </c>
       <c r="AM146" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AN146" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>695</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19256,16 +19257,16 @@
         <v>20</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -19315,7 +19316,7 @@
         <v>20</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19336,7 +19337,7 @@
         <v>20</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>20</v>
@@ -19344,10 +19345,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19370,13 +19371,13 @@
         <v>20</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -19427,7 +19428,7 @@
         <v>20</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19436,19 +19437,19 @@
         <v>88</v>
       </c>
       <c r="AI148" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM148" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK148" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL148" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM148" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>20</v>
@@ -19456,14 +19457,14 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -19485,13 +19486,13 @@
         <v>135</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M149" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N149" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19541,7 +19542,7 @@
         <v>20</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19562,7 +19563,7 @@
         <v>20</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>20</v>
@@ -19570,14 +19571,14 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -19599,16 +19600,16 @@
         <v>135</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M150" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="N150" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O150" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>20</v>
@@ -19657,7 +19658,7 @@
         <v>20</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19686,10 +19687,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19712,13 +19713,13 @@
         <v>20</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="L151" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="L151" t="s" s="2">
+      <c r="M151" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -19769,7 +19770,7 @@
         <v>20</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>88</v>
@@ -19784,24 +19785,24 @@
         <v>100</v>
       </c>
       <c r="AK151" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AL151" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="AL151" t="s" s="2">
+      <c r="AM151" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN151" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>710</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19827,13 +19828,13 @@
         <v>108</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -19862,11 +19863,11 @@
         <v>112</v>
       </c>
       <c r="Y152" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="Z152" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="Z152" t="s" s="2">
-        <v>716</v>
-      </c>
       <c r="AA152" t="s" s="2">
         <v>20</v>
       </c>
@@ -19883,7 +19884,7 @@
         <v>20</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19904,7 +19905,7 @@
         <v>20</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>20</v>
@@ -19912,10 +19913,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19938,16 +19939,16 @@
         <v>20</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -19973,14 +19974,14 @@
         <v>20</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y153" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="Z153" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="Z153" t="s" s="2">
-        <v>723</v>
-      </c>
       <c r="AA153" t="s" s="2">
         <v>20</v>
       </c>
@@ -19997,7 +19998,7 @@
         <v>20</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -20026,10 +20027,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20052,13 +20053,13 @@
         <v>20</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -20109,7 +20110,7 @@
         <v>20</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -20130,7 +20131,7 @@
         <v>20</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>20</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -853,7 +853,7 @@
     <t>Encounter.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KHOrganization)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KAOrganization)
 </t>
   </si>
   <si>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1187,7 +1187,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedPatient)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedBasisPatientKlarname|https://elga.moped.at/StructureDefinition/MopedBasisPatientvbPK)
 </t>
   </si>
   <si>
@@ -2429,7 +2429,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="108.19921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="118.0859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1885,7 +1885,7 @@
     <t>LKF: Transportart</t>
   </si>
   <si>
-    <t>Identifies whether a patient arrives at the reporting facility via ambulance and the type of ambulance that was used.</t>
+    <t>Identifies how the patient arrives at the reporting facility, for example via an ambulance or other mode of transport.</t>
   </si>
   <si>
     <t>Encounter.admission.extension:Transportart.id</t>
